--- a/erp-server/erp-server-file/src/main/resources/excel/oms/kolB2cApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/kolB2cApplicationExport.xlsx
@@ -119,10 +119,10 @@
     <t>{.applyDate}</t>
   </si>
   <si>
-    <t>{.approveStatusNamede}</t>
-  </si>
-  <si>
-    <t>{.invalidStatusNamede}</t>
+    <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.invalidStatusName}</t>
   </si>
   <si>
     <t>{.sampleTypeName}</t>
@@ -1130,8 +1130,8 @@
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="30.125" customWidth="1"/>
+    <col min="4" max="4" width="32.875" customWidth="1"/>
     <col min="5" max="5" width="16.875" customWidth="1"/>
     <col min="6" max="10" width="12.75" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/kolB2cApplicationExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/kolB2cApplicationExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="B2B寄样申请单" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>申请单号</t>
   </si>
@@ -35,6 +35,9 @@
     <t>申请日期</t>
   </si>
   <si>
+    <t>审核状态</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -120,6 +123,9 @@
   </si>
   <si>
     <t>{.approveStatusName}</t>
+  </si>
+  <si>
+    <t>{.billStatusName}</t>
   </si>
   <si>
     <t>{.invalidStatusName}</t>
@@ -1125,34 +1131,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="30.125" customWidth="1"/>
-    <col min="4" max="4" width="32.875" customWidth="1"/>
-    <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="6" max="10" width="12.75" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="18.5" customWidth="1"/>
-    <col min="13" max="13" width="15.375" customWidth="1"/>
-    <col min="14" max="14" width="12.5" customWidth="1"/>
-    <col min="15" max="15" width="13.625" customWidth="1"/>
-    <col min="16" max="16" width="18.25" customWidth="1"/>
-    <col min="17" max="18" width="13.625" customWidth="1"/>
-    <col min="19" max="19" width="17.125" customWidth="1"/>
-    <col min="20" max="20" width="15.625" customWidth="1"/>
-    <col min="21" max="21" width="16.875" customWidth="1"/>
-    <col min="22" max="22" width="14.5" customWidth="1"/>
-    <col min="23" max="23" width="19.75" customWidth="1"/>
-    <col min="24" max="25" width="14.625" customWidth="1"/>
-    <col min="26" max="26" width="15" customWidth="1"/>
-    <col min="27" max="27" width="12.75" customWidth="1"/>
-    <col min="28" max="28" width="15.75" customWidth="1"/>
+    <col min="4" max="5" width="32.875" customWidth="1"/>
+    <col min="6" max="6" width="16.875" customWidth="1"/>
+    <col min="7" max="11" width="12.75" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
+    <col min="13" max="13" width="18.5" customWidth="1"/>
+    <col min="14" max="14" width="15.375" customWidth="1"/>
+    <col min="15" max="15" width="12.5" customWidth="1"/>
+    <col min="16" max="16" width="13.625" customWidth="1"/>
+    <col min="17" max="17" width="18.25" customWidth="1"/>
+    <col min="18" max="19" width="13.625" customWidth="1"/>
+    <col min="20" max="20" width="17.125" customWidth="1"/>
+    <col min="21" max="21" width="15.625" customWidth="1"/>
+    <col min="22" max="22" width="16.875" customWidth="1"/>
+    <col min="23" max="23" width="14.5" customWidth="1"/>
+    <col min="24" max="24" width="19.75" customWidth="1"/>
+    <col min="25" max="26" width="14.625" customWidth="1"/>
+    <col min="27" max="27" width="15" customWidth="1"/>
+    <col min="28" max="28" width="12.75" customWidth="1"/>
+    <col min="29" max="29" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1237,91 +1243,97 @@
       <c r="AB1" t="s">
         <v>27</v>
       </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
